--- a/03_Outputs/all/03_DS/ds_idx4_Capacidad.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx4_Capacidad.xlsx
@@ -393,13 +393,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>4.932057424953441</v>
+        <v>4.932057424953437</v>
       </c>
       <c r="D2">
         <v>10.06622771092133</v>
       </c>
       <c r="E2">
-        <v>0.6194306294860997</v>
+        <v>0.6194306294861032</v>
       </c>
     </row>
     <row r="3">
@@ -414,13 +414,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.1868864167302181</v>
+        <v>-0.186886416730221</v>
       </c>
       <c r="D3">
-        <v>-0.1241773579923564</v>
+        <v>-0.1241773579923556</v>
       </c>
       <c r="E3">
-        <v>1.014194513008875</v>
+        <v>1.014194513008876</v>
       </c>
     </row>
     <row r="4">
@@ -435,13 +435,13 @@
         </is>
       </c>
       <c r="C4">
-        <v>-1.465623666601366</v>
+        <v>-1.465623666601371</v>
       </c>
       <c r="D4">
-        <v>0.04915384490261417</v>
+        <v>0.04915384490261565</v>
       </c>
       <c r="E4">
-        <v>2.048922184700235</v>
+        <v>2.048922184700234</v>
       </c>
     </row>
     <row r="5">
@@ -456,13 +456,13 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.8810916632474853</v>
+        <v>-0.8810916632474872</v>
       </c>
       <c r="D5">
-        <v>0.1991000026886784</v>
+        <v>0.1991000026886788</v>
       </c>
       <c r="E5">
-        <v>0.0291348218938581</v>
+        <v>0.02913482189385769</v>
       </c>
     </row>
     <row r="6">
@@ -477,13 +477,13 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.3513038135589657</v>
+        <v>0.3513038135589637</v>
       </c>
       <c r="D6">
-        <v>-0.1603199057624704</v>
+        <v>-0.1603199057624699</v>
       </c>
       <c r="E6">
-        <v>0.3302708212250268</v>
+        <v>0.330270821225028</v>
       </c>
     </row>
     <row r="7">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.07911312973662882</v>
+        <v>-0.07911312973663079</v>
       </c>
       <c r="D7">
-        <v>-0.04253460707707498</v>
+        <v>-0.04253460707707454</v>
       </c>
       <c r="E7">
-        <v>0.2773577325384</v>
+        <v>0.2773577325384006</v>
       </c>
     </row>
     <row r="8">
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.2835813641125887</v>
+        <v>0.2835813641125875</v>
       </c>
       <c r="D8">
-        <v>-0.07009905033084607</v>
+        <v>-0.07009905033084589</v>
       </c>
       <c r="E8">
-        <v>-0.1619007795050866</v>
+        <v>-0.1619007795050855</v>
       </c>
     </row>
     <row r="9">
@@ -540,13 +540,13 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.4360327112206269</v>
+        <v>0.4360327112206236</v>
       </c>
       <c r="D9">
-        <v>-0.42604850484496</v>
+        <v>-0.4260485048449593</v>
       </c>
       <c r="E9">
-        <v>1.14747720564196</v>
+        <v>1.147477205641962</v>
       </c>
     </row>
     <row r="10">
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C10">
-        <v>0.2943671636949721</v>
+        <v>0.2943671636949705</v>
       </c>
       <c r="D10">
-        <v>-0.1144184353824097</v>
+        <v>-0.1144184353824094</v>
       </c>
       <c r="E10">
-        <v>0.1186289548949663</v>
+        <v>0.1186289548949674</v>
       </c>
     </row>
     <row r="11">
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="C11">
-        <v>-1.065021908663941</v>
+        <v>-1.065021908663944</v>
       </c>
       <c r="D11">
-        <v>0.1667843464686987</v>
+        <v>0.1667843464686993</v>
       </c>
       <c r="E11">
-        <v>0.5643457166417374</v>
+        <v>0.5643457166417367</v>
       </c>
     </row>
     <row r="12">
@@ -603,13 +603,13 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.7493506638061876</v>
+        <v>0.7493506638061864</v>
       </c>
       <c r="D12">
-        <v>-0.3168414831165388</v>
+        <v>-0.3168414831165386</v>
       </c>
       <c r="E12">
-        <v>-0.1297660299662778</v>
+        <v>-0.129766029966276</v>
       </c>
     </row>
     <row r="13">
@@ -624,13 +624,13 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.6731851743877807</v>
+        <v>-0.6731851743877822</v>
       </c>
       <c r="D13">
-        <v>0.1614722658482508</v>
+        <v>0.1614722658482511</v>
       </c>
       <c r="E13">
-        <v>-0.07534302891717758</v>
+        <v>-0.07534302891717787</v>
       </c>
     </row>
     <row r="14">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.4777313494366484</v>
+        <v>0.4777313494366493</v>
       </c>
       <c r="D14">
-        <v>-0.2946502561227994</v>
+        <v>-0.2946502561228002</v>
       </c>
       <c r="E14">
-        <v>-1.471659221462269</v>
+        <v>-1.471659221462267</v>
       </c>
     </row>
     <row r="15">
@@ -666,13 +666,13 @@
         </is>
       </c>
       <c r="C15">
-        <v>-1.579541660537029</v>
+        <v>-1.579541660537031</v>
       </c>
       <c r="D15">
-        <v>0.3571596374948954</v>
+        <v>0.3571596374948959</v>
       </c>
       <c r="E15">
-        <v>0.1664973961432468</v>
+        <v>0.1664973961432453</v>
       </c>
     </row>
     <row r="16">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.8981250231030836</v>
+        <v>-0.8981250231030848</v>
       </c>
       <c r="D16">
-        <v>0.2553958471021331</v>
+        <v>0.2553958471021333</v>
       </c>
       <c r="E16">
-        <v>-0.3214566070830642</v>
+        <v>-0.3214566070830649</v>
       </c>
     </row>
     <row r="17">
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="C17">
-        <v>0.2284406598357731</v>
+        <v>0.2284406598357712</v>
       </c>
       <c r="D17">
-        <v>-0.1260224100461345</v>
+        <v>-0.1260224100461341</v>
       </c>
       <c r="E17">
-        <v>0.3106074961692476</v>
+        <v>0.3106074961692487</v>
       </c>
     </row>
     <row r="18">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.1910417792420634</v>
+        <v>0.1910417792420641</v>
       </c>
       <c r="D18">
-        <v>-0.1083388910842045</v>
+        <v>-0.1083388910842051</v>
       </c>
       <c r="E18">
         <v>-1.404666839085759</v>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C19">
-        <v>-0.09696952164368311</v>
+        <v>-0.09696952164368486</v>
       </c>
       <c r="D19">
-        <v>-0.01682719997359611</v>
+        <v>-0.01682719997359575</v>
       </c>
       <c r="E19">
-        <v>0.1346358110162376</v>
+        <v>0.1346358110162382</v>
       </c>
     </row>
     <row r="20">
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.8211757724635933</v>
+        <v>0.8211757724635931</v>
       </c>
       <c r="D20">
-        <v>-0.7554550707594797</v>
+        <v>-0.7554550707594803</v>
       </c>
       <c r="E20">
-        <v>-0.6140602781473697</v>
+        <v>-0.6140602781473679</v>
       </c>
     </row>
     <row r="21">
@@ -792,13 +792,13 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.2626739501041312</v>
+        <v>0.2626739501041296</v>
       </c>
       <c r="D21">
-        <v>-0.1001484336684963</v>
+        <v>-0.100148433668496</v>
       </c>
       <c r="E21">
-        <v>0.07695673619539858</v>
+        <v>0.07695673619539961</v>
       </c>
     </row>
     <row r="22">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="C22">
-        <v>-0.9937111687894344</v>
+        <v>-0.993711168789436</v>
       </c>
       <c r="D22">
-        <v>0.2446857587994612</v>
+        <v>0.2446857587994615</v>
       </c>
       <c r="E22">
-        <v>-0.08437681243440967</v>
+        <v>-0.08437681243441031</v>
       </c>
     </row>
     <row r="23">
@@ -834,13 +834,13 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.4071108975450219</v>
+        <v>0.4071108975450208</v>
       </c>
       <c r="D23">
-        <v>-0.0825158261267934</v>
+        <v>-0.0825158261267933</v>
       </c>
       <c r="E23">
-        <v>-0.2910658821150636</v>
+        <v>-0.2910658821150624</v>
       </c>
     </row>
     <row r="24">
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="C24">
-        <v>-0.5001627391680625</v>
+        <v>-0.5001627391680651</v>
       </c>
       <c r="D24">
-        <v>0.02246819044321164</v>
+        <v>0.02246819044321226</v>
       </c>
       <c r="E24">
-        <v>0.5645399851326455</v>
+        <v>0.5645399851326457</v>
       </c>
     </row>
     <row r="25">
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="C25">
-        <v>1.279430352603479</v>
+        <v>1.279430352603477</v>
       </c>
       <c r="D25">
-        <v>-0.397651331744457</v>
+        <v>-0.3976513317444567</v>
       </c>
       <c r="E25">
-        <v>0.3319662439528154</v>
+        <v>0.331966243952818</v>
       </c>
     </row>
     <row r="26">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="C26">
-        <v>-0.4328442276739216</v>
+        <v>-0.4328442276739235</v>
       </c>
       <c r="D26">
-        <v>0.05812957162657147</v>
+        <v>0.05812957162657188</v>
       </c>
       <c r="E26">
-        <v>0.2077908928812835</v>
+        <v>0.2077908928812836</v>
       </c>
     </row>
     <row r="27">
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="C27">
-        <v>-1.144193426265558</v>
+        <v>-1.14419342626556</v>
       </c>
       <c r="D27">
-        <v>0.2070529622707039</v>
+        <v>0.2070529622707045</v>
       </c>
       <c r="E27">
-        <v>0.4290554467824251</v>
+        <v>0.4290554467824242</v>
       </c>
     </row>
     <row r="28">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C28">
-        <v>1.050911694481208</v>
+        <v>1.050911694481205</v>
       </c>
       <c r="D28">
-        <v>-0.8290756910795971</v>
+        <v>-0.8290756910795964</v>
       </c>
       <c r="E28">
-        <v>1.147153942629938</v>
+        <v>1.14715394262994</v>
       </c>
     </row>
     <row r="29">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="C29">
-        <v>-1.086655413839681</v>
+        <v>-1.086655413839684</v>
       </c>
       <c r="D29">
-        <v>0.1858835897805476</v>
+        <v>0.1858835897805483</v>
       </c>
       <c r="E29">
-        <v>0.472736169504351</v>
+        <v>0.4727361695043503</v>
       </c>
     </row>
     <row r="30">
@@ -981,13 +981,13 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.3212343415909837</v>
+        <v>0.3212343415909806</v>
       </c>
       <c r="D30">
-        <v>-0.2861522559304094</v>
+        <v>-0.2861522559304086</v>
       </c>
       <c r="E30">
-        <v>1.231392144432034</v>
+        <v>1.231392144432036</v>
       </c>
     </row>
     <row r="31">
@@ -1002,13 +1002,13 @@
         </is>
       </c>
       <c r="C31">
-        <v>-1.122158891932793</v>
+        <v>-1.122158891932794</v>
       </c>
       <c r="D31">
-        <v>0.3848345990924912</v>
+        <v>0.3848345990924911</v>
       </c>
       <c r="E31">
-        <v>-0.8088347044861663</v>
+        <v>-0.8088347044861675</v>
       </c>
     </row>
     <row r="32">
@@ -1023,13 +1023,13 @@
         </is>
       </c>
       <c r="C32">
-        <v>-0.1068224020365251</v>
+        <v>-0.1068224020365295</v>
       </c>
       <c r="D32">
-        <v>-0.268758980718838</v>
+        <v>-0.2687589807188366</v>
       </c>
       <c r="E32">
-        <v>1.851985958974155</v>
+        <v>1.851985958974156</v>
       </c>
     </row>
     <row r="33">
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.1070218933831298</v>
+        <v>0.107021893383129</v>
       </c>
       <c r="D33">
         <v>0.02348350784099072</v>
       </c>
       <c r="E33">
-        <v>-0.4891223196987469</v>
+        <v>-0.4891223196987462</v>
       </c>
     </row>
     <row r="34">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="C34">
-        <v>1.53376376214219</v>
+        <v>1.533763762142191</v>
       </c>
       <c r="D34">
-        <v>-0.5599793388049913</v>
+        <v>-0.5599793388049921</v>
       </c>
       <c r="E34">
-        <v>-1.501513825863744</v>
+        <v>-1.501513825863742</v>
       </c>
     </row>
     <row r="35">
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="C35">
-        <v>-3.431532997557505</v>
+        <v>-3.431532997557504</v>
       </c>
       <c r="D35">
-        <v>1.156512413494117</v>
+        <v>1.156512413494116</v>
       </c>
       <c r="E35">
-        <v>-2.035670863050599</v>
+        <v>-2.035670863050604</v>
       </c>
     </row>
     <row r="36">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="C36">
-        <v>-0.5846175360354764</v>
+        <v>-0.5846175360354779</v>
       </c>
       <c r="D36">
-        <v>0.007816906295004001</v>
+        <v>0.007816906295004235</v>
       </c>
       <c r="E36">
-        <v>-0.02117080141104028</v>
+        <v>-0.02117080141104044</v>
       </c>
     </row>
     <row r="37">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C37">
-        <v>-0.224240437459071</v>
+        <v>-0.2242404374590737</v>
       </c>
       <c r="D37">
-        <v>-0.06371695016729041</v>
+        <v>-0.06371695016728977</v>
       </c>
       <c r="E37">
-        <v>0.6705287919470737</v>
+        <v>0.6705287919470744</v>
       </c>
     </row>
     <row r="38">
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="C38">
-        <v>-0.07414977299289191</v>
+        <v>-0.07414977299289396</v>
       </c>
       <c r="D38">
-        <v>-0.04963953562546592</v>
+        <v>-0.04963953562546547</v>
       </c>
       <c r="E38">
-        <v>0.3167540158293946</v>
+        <v>0.3167540158293953</v>
       </c>
     </row>
     <row r="39">
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="C39">
-        <v>-0.1314174280221801</v>
+        <v>-0.131417428022181</v>
       </c>
       <c r="D39">
-        <v>0.08138669224887207</v>
+        <v>0.08138669224887211</v>
       </c>
       <c r="E39">
-        <v>-0.4688497903931246</v>
+        <v>-0.4688497903931242</v>
       </c>
     </row>
     <row r="40">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="C40">
-        <v>1.022348912944775</v>
+        <v>1.022348912944772</v>
       </c>
       <c r="D40">
-        <v>-0.4234218003341215</v>
+        <v>-0.4234218003341207</v>
       </c>
       <c r="E40">
-        <v>0.9491171655458275</v>
+        <v>0.9491171655458299</v>
       </c>
     </row>
     <row r="41">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="C41">
-        <v>-0.2737153260270224</v>
+        <v>-0.2737153260270236</v>
       </c>
       <c r="D41">
-        <v>0.0828231276704807</v>
+        <v>0.08282312767048086</v>
       </c>
       <c r="E41">
-        <v>-0.2332176849867619</v>
+        <v>-0.2332176849867616</v>
       </c>
     </row>
     <row r="42">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.9788951914100446</v>
+        <v>0.9788951914100422</v>
       </c>
       <c r="D42">
-        <v>-0.7599229511837144</v>
+        <v>-0.759922951183714</v>
       </c>
       <c r="E42">
-        <v>0.8045805071626104</v>
+        <v>0.8045805071626131</v>
       </c>
     </row>
     <row r="43">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="C43">
-        <v>0.1371607466419728</v>
+        <v>0.1371607466419706</v>
       </c>
       <c r="D43">
-        <v>-0.1233752969496431</v>
+        <v>-0.1233752969496426</v>
       </c>
       <c r="E43">
-        <v>0.4501114087256441</v>
+        <v>0.4501114087256451</v>
       </c>
     </row>
     <row r="44">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="C44">
-        <v>1.411341843620977</v>
+        <v>1.411341843620974</v>
       </c>
       <c r="D44">
-        <v>-0.4789193836254648</v>
+        <v>-0.4789193836254642</v>
       </c>
       <c r="E44">
-        <v>0.653048306788691</v>
+        <v>0.6530483067886939</v>
       </c>
     </row>
     <row r="45">
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="C45">
-        <v>0.08983097960590207</v>
+        <v>0.08983097960590039</v>
       </c>
       <c r="D45">
-        <v>-0.06237589729355155</v>
+        <v>-0.06237589729355122</v>
       </c>
       <c r="E45">
-        <v>0.1200064392920758</v>
+        <v>0.1200064392920767</v>
       </c>
     </row>
     <row r="46">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="C46">
-        <v>-0.2151588572943402</v>
+        <v>-0.215158857294343</v>
       </c>
       <c r="D46">
-        <v>-0.08686701893873512</v>
+        <v>-0.08686701893873439</v>
       </c>
       <c r="E46">
-        <v>0.8111185798619727</v>
+        <v>0.8111185798619732</v>
       </c>
     </row>
     <row r="47">
@@ -1338,13 +1338,13 @@
         </is>
       </c>
       <c r="C47">
-        <v>0.4383729094698351</v>
+        <v>0.4383729094698345</v>
       </c>
       <c r="D47">
-        <v>-0.05560394323931343</v>
+        <v>-0.05560394323931346</v>
       </c>
       <c r="E47">
-        <v>-0.5265991875080011</v>
+        <v>-0.5265991875079998</v>
       </c>
     </row>
     <row r="48">
@@ -1362,10 +1362,10 @@
         <v>2.595048795971749</v>
       </c>
       <c r="D48">
-        <v>-1.191196484381736</v>
+        <v>-1.191196484381737</v>
       </c>
       <c r="E48">
-        <v>-0.7313355554974549</v>
+        <v>-0.7313355554974506</v>
       </c>
     </row>
     <row r="49">
@@ -1380,13 +1380,13 @@
         </is>
       </c>
       <c r="C49">
-        <v>-0.4754787392036915</v>
+        <v>-0.4754787392036924</v>
       </c>
       <c r="D49">
-        <v>0.1725572714744083</v>
+        <v>0.1725572714744084</v>
       </c>
       <c r="E49">
-        <v>-0.4910125538812022</v>
+        <v>-0.4910125538812023</v>
       </c>
     </row>
     <row r="50">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="C50">
-        <v>-0.3875772233231933</v>
+        <v>-0.3875772233231939</v>
       </c>
       <c r="D50">
         <v>0.1681310576331979</v>
@@ -1422,13 +1422,13 @@
         </is>
       </c>
       <c r="C51">
-        <v>-0.3554195998847738</v>
+        <v>-0.3554195998847759</v>
       </c>
       <c r="D51">
-        <v>0.02150934190088533</v>
+        <v>0.0215093419008858</v>
       </c>
       <c r="E51">
-        <v>0.3214688122941636</v>
+        <v>0.3214688122941639</v>
       </c>
     </row>
     <row r="52">
@@ -1446,10 +1446,10 @@
         <v>0.6328788745981155</v>
       </c>
       <c r="D52">
-        <v>-0.5455209776202269</v>
+        <v>-0.5455209776202273</v>
       </c>
       <c r="E52">
-        <v>-0.8761375420072915</v>
+        <v>-0.87613754200729</v>
       </c>
     </row>
     <row r="53">
@@ -1464,13 +1464,13 @@
         </is>
       </c>
       <c r="C53">
-        <v>0.03362476520160302</v>
+        <v>0.03362476520160221</v>
       </c>
       <c r="D53">
-        <v>0.03607317724220359</v>
+        <v>0.03607317724220362</v>
       </c>
       <c r="E53">
-        <v>-0.4475543197778106</v>
+        <v>-0.44755431977781</v>
       </c>
     </row>
     <row r="54">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="C54">
-        <v>-0.7769487989895534</v>
+        <v>-0.7769487989895573</v>
       </c>
       <c r="D54">
-        <v>-0.05136686357560638</v>
+        <v>-0.05136686357560523</v>
       </c>
       <c r="E54">
         <v>1.540064780003684</v>
@@ -1506,13 +1506,13 @@
         </is>
       </c>
       <c r="C55">
-        <v>0.08972707204168744</v>
+        <v>0.08972707204168462</v>
       </c>
       <c r="D55">
-        <v>-0.1704897554471928</v>
+        <v>-0.1704897554471921</v>
       </c>
       <c r="E55">
-        <v>0.849878544048981</v>
+        <v>0.849878544048982</v>
       </c>
     </row>
     <row r="56">
@@ -1530,10 +1530,10 @@
         <v>2.060223938241901</v>
       </c>
       <c r="D56">
-        <v>-0.9217652993640906</v>
+        <v>-0.9217652993640911</v>
       </c>
       <c r="E56">
-        <v>-0.7975490879715081</v>
+        <v>-0.7975490879715049</v>
       </c>
     </row>
     <row r="57">
@@ -1548,13 +1548,13 @@
         </is>
       </c>
       <c r="C57">
-        <v>0.8044526780947582</v>
+        <v>0.8044526780947583</v>
       </c>
       <c r="D57">
-        <v>-0.07716425581761491</v>
+        <v>-0.07716425581761523</v>
       </c>
       <c r="E57">
-        <v>-1.012217728051116</v>
+        <v>-1.012217728051114</v>
       </c>
     </row>
     <row r="58">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="C58">
-        <v>-1.145720540257349</v>
+        <v>-1.145720540257351</v>
       </c>
       <c r="D58">
-        <v>0.2661459541119431</v>
+        <v>0.2661459541119434</v>
       </c>
       <c r="E58">
-        <v>0.03285186474766858</v>
+        <v>0.03285186474766766</v>
       </c>
     </row>
     <row r="59">
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="C59">
-        <v>0.4964656939693272</v>
+        <v>0.4964656939693263</v>
       </c>
       <c r="D59">
-        <v>-0.09858583001720797</v>
+        <v>-0.09858583001720791</v>
       </c>
       <c r="E59">
-        <v>-0.3366556900260534</v>
+        <v>-0.3366556900260521</v>
       </c>
     </row>
     <row r="60">
@@ -1614,10 +1614,10 @@
         <v>2.936801907162732</v>
       </c>
       <c r="D60">
-        <v>-1.323615229381038</v>
+        <v>-1.323615229381039</v>
       </c>
       <c r="E60">
-        <v>-0.4267970826902391</v>
+        <v>-0.4267970826902341</v>
       </c>
     </row>
     <row r="61">
@@ -1632,13 +1632,13 @@
         </is>
       </c>
       <c r="C61">
-        <v>-0.6254226690401042</v>
+        <v>-0.6254226690401075</v>
       </c>
       <c r="D61">
-        <v>-0.01129257648809805</v>
+        <v>-0.01129257648809719</v>
       </c>
       <c r="E61">
-        <v>1.008354490042982</v>
+        <v>1.008354490042983</v>
       </c>
     </row>
     <row r="62">
@@ -1653,13 +1653,13 @@
         </is>
       </c>
       <c r="C62">
-        <v>0.7691115778690941</v>
+        <v>0.7691115778690928</v>
       </c>
       <c r="D62">
-        <v>-0.2090281782202741</v>
+        <v>-0.2090281782202739</v>
       </c>
       <c r="E62">
-        <v>-0.06129901916476832</v>
+        <v>-0.06129901916476654</v>
       </c>
     </row>
     <row r="63">
@@ -1674,13 +1674,13 @@
         </is>
       </c>
       <c r="C63">
-        <v>0.585419315340227</v>
+        <v>0.5854193153402247</v>
       </c>
       <c r="D63">
-        <v>-0.2525207369189389</v>
+        <v>-0.2525207369189384</v>
       </c>
       <c r="E63">
-        <v>0.548937862317276</v>
+        <v>0.5489378623172776</v>
       </c>
     </row>
     <row r="64">
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="C64">
-        <v>2.164626286153231</v>
+        <v>2.164626286153232</v>
       </c>
       <c r="D64">
-        <v>-0.8627696013849353</v>
+        <v>-0.8627696013849362</v>
       </c>
       <c r="E64">
-        <v>-1.375722464422056</v>
+        <v>-1.375722464422053</v>
       </c>
     </row>
     <row r="65">
@@ -1716,13 +1716,13 @@
         </is>
       </c>
       <c r="C65">
-        <v>0.7212570449489897</v>
+        <v>0.7212570449489868</v>
       </c>
       <c r="D65">
-        <v>-0.8645136869694725</v>
+        <v>-0.8645136869694718</v>
       </c>
       <c r="E65">
-        <v>1.124472890690183</v>
+        <v>1.124472890690185</v>
       </c>
     </row>
     <row r="66">
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="C66">
-        <v>0.5457243921369299</v>
+        <v>0.5457243921369297</v>
       </c>
       <c r="D66">
-        <v>-0.0577985052098907</v>
+        <v>-0.05779850520989083</v>
       </c>
       <c r="E66">
-        <v>-0.6968655067163696</v>
+        <v>-0.6968655067163684</v>
       </c>
     </row>
     <row r="67">
@@ -1758,13 +1758,13 @@
         </is>
       </c>
       <c r="C67">
-        <v>2.244968043559918</v>
+        <v>2.244968043559917</v>
       </c>
       <c r="D67">
         <v>-0.5781960871675376</v>
       </c>
       <c r="E67">
-        <v>-0.1141069245945281</v>
+        <v>-0.1141069245945243</v>
       </c>
     </row>
     <row r="68">
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="C68">
-        <v>-0.4558834384534594</v>
+        <v>-0.455883438453461</v>
       </c>
       <c r="D68">
-        <v>0.10049142857799</v>
+        <v>0.1004914285779903</v>
       </c>
       <c r="E68">
-        <v>-0.03840154384846493</v>
+        <v>-0.03840154384846489</v>
       </c>
     </row>
     <row r="69">
@@ -1800,13 +1800,13 @@
         </is>
       </c>
       <c r="C69">
-        <v>0.8119258261351793</v>
+        <v>0.8119258261351774</v>
       </c>
       <c r="D69">
-        <v>-0.2796310861072982</v>
+        <v>-0.2796310861072978</v>
       </c>
       <c r="E69">
-        <v>0.3414078451227627</v>
+        <v>0.3414078451227646</v>
       </c>
     </row>
     <row r="70">
@@ -1821,13 +1821,13 @@
         </is>
       </c>
       <c r="C70">
-        <v>-0.4092155481601828</v>
+        <v>-0.409215548160184</v>
       </c>
       <c r="D70">
         <v>-0.125638013014505</v>
       </c>
       <c r="E70">
-        <v>-0.2530431771495862</v>
+        <v>-0.2530431771495861</v>
       </c>
     </row>
     <row r="71">
@@ -1845,10 +1845,10 @@
         <v>-1.92630437648288</v>
       </c>
       <c r="D71">
-        <v>0.6532840254124079</v>
+        <v>0.6532840254124078</v>
       </c>
       <c r="E71">
-        <v>-1.234302974820323</v>
+        <v>-1.234302974820325</v>
       </c>
     </row>
     <row r="72">
@@ -1863,13 +1863,13 @@
         </is>
       </c>
       <c r="C72">
-        <v>-1.608786946546618</v>
+        <v>-1.60878694654662</v>
       </c>
       <c r="D72">
-        <v>0.3702185349177793</v>
+        <v>0.3702185349177798</v>
       </c>
       <c r="E72">
-        <v>0.1287789636202591</v>
+        <v>0.1287789636202575</v>
       </c>
     </row>
     <row r="73">
@@ -1884,13 +1884,13 @@
         </is>
       </c>
       <c r="C73">
-        <v>-0.9606054705816323</v>
+        <v>-0.960605470581635</v>
       </c>
       <c r="D73">
-        <v>0.1345216456871969</v>
+        <v>0.1345216456871975</v>
       </c>
       <c r="E73">
-        <v>0.602078444448928</v>
+        <v>0.6020784444489276</v>
       </c>
     </row>
     <row r="74">
@@ -1905,13 +1905,13 @@
         </is>
       </c>
       <c r="C74">
-        <v>-1.726820386184193</v>
+        <v>-1.726820386184197</v>
       </c>
       <c r="D74">
-        <v>0.2261327198959643</v>
+        <v>0.2261327198959655</v>
       </c>
       <c r="E74">
-        <v>1.304751672310705</v>
+        <v>1.304751672310704</v>
       </c>
     </row>
     <row r="75">
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="C75">
-        <v>-0.3463217978672357</v>
+        <v>-0.3463217978672373</v>
       </c>
       <c r="D75">
-        <v>0.07069281987228947</v>
+        <v>0.07069281987228976</v>
       </c>
       <c r="E75">
-        <v>-0.02617024168752507</v>
+        <v>-0.02617024168752491</v>
       </c>
     </row>
     <row r="76">
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="C76">
-        <v>-1.038850203745132</v>
+        <v>-1.038850203745135</v>
       </c>
       <c r="D76">
-        <v>0.1008643016372914</v>
+        <v>0.1008643016372923</v>
       </c>
       <c r="E76">
-        <v>0.9641389127184745</v>
+        <v>0.9641389127184741</v>
       </c>
     </row>
     <row r="77">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="C77">
-        <v>-1.311064577494593</v>
+        <v>-1.311064577494595</v>
       </c>
       <c r="D77">
-        <v>0.256451871818443</v>
+        <v>0.2564518718184436</v>
       </c>
       <c r="E77">
-        <v>0.3833396127958504</v>
+        <v>0.3833396127958493</v>
       </c>
     </row>
     <row r="78">
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="C78">
-        <v>0.5797652200803589</v>
+        <v>0.5797652200803576</v>
       </c>
       <c r="D78">
-        <v>-0.1628751130313642</v>
+        <v>-0.162875113031364</v>
       </c>
       <c r="E78">
-        <v>-0.04635955363138491</v>
+        <v>-0.04635955363138339</v>
       </c>
     </row>
     <row r="79">
@@ -2010,13 +2010,13 @@
         </is>
       </c>
       <c r="C79">
-        <v>-0.4065861824249212</v>
+        <v>-0.4065861824249228</v>
       </c>
       <c r="D79">
-        <v>0.0806633364273856</v>
+        <v>0.08066333642738591</v>
       </c>
       <c r="E79">
-        <v>0.01043385469189246</v>
+        <v>0.01043385469189256</v>
       </c>
     </row>
     <row r="80">
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="C80">
-        <v>-0.4858411537777267</v>
+        <v>-0.4858411537777286</v>
       </c>
       <c r="D80">
-        <v>0.07979604059131966</v>
+        <v>0.07979604059132006</v>
       </c>
       <c r="E80">
         <v>0.1529261092625088</v>
@@ -2052,13 +2052,13 @@
         </is>
       </c>
       <c r="C81">
-        <v>-0.137460735716551</v>
+        <v>-0.1374607357165528</v>
       </c>
       <c r="D81">
-        <v>-0.001542773325809898</v>
+        <v>-0.001542773325809555</v>
       </c>
       <c r="E81">
-        <v>0.1012850238308308</v>
+        <v>0.1012850238308313</v>
       </c>
     </row>
     <row r="82">
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="C82">
-        <v>-0.1948969078024478</v>
+        <v>-0.1948969078024488</v>
       </c>
       <c r="D82">
-        <v>0.0823503771636227</v>
+        <v>0.08235037716362278</v>
       </c>
       <c r="E82">
-        <v>-0.3659129291630805</v>
+        <v>-0.3659129291630803</v>
       </c>
     </row>
     <row r="83">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="C83">
-        <v>1.254584376069544</v>
+        <v>1.254584376069543</v>
       </c>
       <c r="D83">
-        <v>-0.3386315561631243</v>
+        <v>-0.3386315561631241</v>
       </c>
       <c r="E83">
-        <v>-0.02354056505263129</v>
+        <v>-0.0235405650526288</v>
       </c>
     </row>
     <row r="84">
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="C84">
-        <v>-1.685512459480697</v>
+        <v>-1.685512459480699</v>
       </c>
       <c r="D84">
-        <v>0.3541764004280605</v>
+        <v>0.3541764004280611</v>
       </c>
       <c r="E84">
-        <v>0.3693298874889074</v>
+        <v>0.3693298874889058</v>
       </c>
     </row>
     <row r="85">
@@ -2136,13 +2136,13 @@
         </is>
       </c>
       <c r="C85">
-        <v>1.541616721730588</v>
+        <v>1.541616721730587</v>
       </c>
       <c r="D85">
-        <v>-0.7395525730681912</v>
+        <v>-0.7395525730681914</v>
       </c>
       <c r="E85">
-        <v>-0.3030588314933099</v>
+        <v>-0.303058831493307</v>
       </c>
     </row>
     <row r="86">
@@ -2157,13 +2157,13 @@
         </is>
       </c>
       <c r="C86">
-        <v>2.733535181246051</v>
+        <v>2.733535181246052</v>
       </c>
       <c r="D86">
         <v>-1.241928229051168</v>
       </c>
       <c r="E86">
-        <v>-0.6276875897056173</v>
+        <v>-0.6276875897056129</v>
       </c>
     </row>
     <row r="87">
@@ -2178,13 +2178,13 @@
         </is>
       </c>
       <c r="C87">
-        <v>-1.065525630258566</v>
+        <v>-1.065525630258567</v>
       </c>
       <c r="D87">
-        <v>0.3005542884208442</v>
+        <v>0.3005542884208444</v>
       </c>
       <c r="E87">
-        <v>-0.337639442530553</v>
+        <v>-0.3376394425305539</v>
       </c>
     </row>
     <row r="88">
@@ -2199,13 +2199,13 @@
         </is>
       </c>
       <c r="C88">
-        <v>2.085250285057611</v>
+        <v>2.085250285057614</v>
       </c>
       <c r="D88">
-        <v>-0.8213916250620219</v>
+        <v>-0.8213916250620235</v>
       </c>
       <c r="E88">
-        <v>-2.348347630090543</v>
+        <v>-2.34834763009054</v>
       </c>
     </row>
     <row r="89">
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="C89">
-        <v>-0.02708369975589459</v>
+        <v>-0.02708369975589619</v>
       </c>
       <c r="D89">
-        <v>-0.02055406969934166</v>
+        <v>-0.02055406969934136</v>
       </c>
       <c r="E89">
-        <v>0.03930373582545499</v>
+        <v>0.03930373582545565</v>
       </c>
     </row>
     <row r="90">
@@ -2241,13 +2241,13 @@
         </is>
       </c>
       <c r="C90">
-        <v>-0.7794331416105736</v>
+        <v>-0.7794331416105762</v>
       </c>
       <c r="D90">
-        <v>0.1028450706625865</v>
+        <v>0.1028450706625871</v>
       </c>
       <c r="E90">
-        <v>0.5035251298480287</v>
+        <v>0.5035251298480286</v>
       </c>
     </row>
     <row r="91">
@@ -2262,13 +2262,13 @@
         </is>
       </c>
       <c r="C91">
-        <v>-0.2817900766653327</v>
+        <v>-0.2817900766653349</v>
       </c>
       <c r="D91">
-        <v>-0.007351234235421639</v>
+        <v>-0.007351234235421132</v>
       </c>
       <c r="E91">
-        <v>0.3893174004750597</v>
+        <v>0.3893174004750601</v>
       </c>
     </row>
     <row r="92">
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="C92">
-        <v>0.3007750963947731</v>
+        <v>0.3007750963947725</v>
       </c>
       <c r="D92">
-        <v>-0.01673108319926258</v>
+        <v>-0.01673108319926261</v>
       </c>
       <c r="E92">
-        <v>-0.5517399047527036</v>
+        <v>-0.5517399047527026</v>
       </c>
     </row>
     <row r="93">
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="C93">
-        <v>0.9125337693928055</v>
+        <v>0.9125337693928056</v>
       </c>
       <c r="D93">
-        <v>-0.1106739301653177</v>
+        <v>-0.1106739301653181</v>
       </c>
       <c r="E93">
-        <v>-0.9723868032504611</v>
+        <v>-0.9723868032504595</v>
       </c>
     </row>
     <row r="94">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="C94">
-        <v>-1.35336580484087</v>
+        <v>-1.353365804840872</v>
       </c>
       <c r="D94">
-        <v>0.3357203444784829</v>
+        <v>0.3357203444784833</v>
       </c>
       <c r="E94">
-        <v>-0.07873822369834711</v>
+        <v>-0.07873822369834826</v>
       </c>
     </row>
     <row r="95">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="C95">
-        <v>0.3290388423147813</v>
+        <v>0.3290388423147804</v>
       </c>
       <c r="D95">
-        <v>-0.05708263443800312</v>
+        <v>-0.05708263443800304</v>
       </c>
       <c r="E95">
-        <v>-0.3281229254551983</v>
+        <v>-0.3281229254551973</v>
       </c>
     </row>
     <row r="96">
@@ -2367,13 +2367,13 @@
         </is>
       </c>
       <c r="C96">
-        <v>-0.1010016461604244</v>
+        <v>-0.1010016461604268</v>
       </c>
       <c r="D96">
-        <v>-0.07978224811034376</v>
+        <v>-0.07978224811034318</v>
       </c>
       <c r="E96">
-        <v>0.5664899138858209</v>
+        <v>0.5664899138858217</v>
       </c>
     </row>
     <row r="97">
@@ -2394,7 +2394,7 @@
         <v>1.235902717668685</v>
       </c>
       <c r="E97">
-        <v>-1.413710797187754</v>
+        <v>-1.41371079718776</v>
       </c>
     </row>
     <row r="98">
@@ -2409,13 +2409,13 @@
         </is>
       </c>
       <c r="C98">
-        <v>-0.04707617454422576</v>
+        <v>-0.04707617454422836</v>
       </c>
       <c r="D98">
-        <v>-0.1144256124324588</v>
+        <v>-0.1144256124324582</v>
       </c>
       <c r="E98">
-        <v>0.7073388213787327</v>
+        <v>0.7073388213787335</v>
       </c>
     </row>
     <row r="99">
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="C99">
-        <v>0.7108776742147652</v>
+        <v>0.7108776742147636</v>
       </c>
       <c r="D99">
-        <v>-0.2366407307462175</v>
+        <v>-0.2366407307462172</v>
       </c>
       <c r="E99">
-        <v>0.2254638935271247</v>
+        <v>0.2254638935271264</v>
       </c>
     </row>
     <row r="100">
@@ -2451,13 +2451,13 @@
         </is>
       </c>
       <c r="C100">
-        <v>0.1802991598168338</v>
+        <v>0.180299159816833</v>
       </c>
       <c r="D100">
-        <v>0.01061882460853396</v>
+        <v>0.01061882460853393</v>
       </c>
       <c r="E100">
-        <v>-0.5286275222549235</v>
+        <v>-0.5286275222549227</v>
       </c>
     </row>
     <row r="101">
@@ -2472,13 +2472,13 @@
         </is>
       </c>
       <c r="C101">
-        <v>0.4218535202270241</v>
+        <v>0.4218535202270223</v>
       </c>
       <c r="D101">
-        <v>-0.1710983379301233</v>
+        <v>-0.1710983379301229</v>
       </c>
       <c r="E101">
-        <v>0.281387300175787</v>
+        <v>0.2813873001757884</v>
       </c>
     </row>
     <row r="102">
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="C102">
-        <v>-1.665044331204878</v>
+        <v>-1.665044331204877</v>
       </c>
       <c r="D102">
-        <v>0.6744261320830911</v>
+        <v>0.6744261320830905</v>
       </c>
       <c r="E102">
-        <v>-1.827419765521797</v>
+        <v>-1.827419765521799</v>
       </c>
     </row>
     <row r="103">
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="C103">
-        <v>-0.415159316369589</v>
+        <v>-0.4151593163695916</v>
       </c>
       <c r="D103">
-        <v>-0.1417230407558747</v>
+        <v>-0.1417230407558741</v>
       </c>
       <c r="E103">
-        <v>0.6959668254881735</v>
+        <v>0.6959668254881738</v>
       </c>
     </row>
     <row r="104">
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="C104">
-        <v>0.02611263727860212</v>
+        <v>0.0261126372785993</v>
       </c>
       <c r="D104">
-        <v>-0.1570827053349622</v>
+        <v>-0.1570827053349615</v>
       </c>
       <c r="E104">
-        <v>0.8690640564663168</v>
+        <v>0.8690640564663177</v>
       </c>
     </row>
     <row r="105">
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="C105">
-        <v>0.6867342658353349</v>
+        <v>0.6867342658353337</v>
       </c>
       <c r="D105">
-        <v>-0.1917510250127472</v>
+        <v>-0.191751025012747</v>
       </c>
       <c r="E105">
-        <v>-0.0358860762926549</v>
+        <v>-0.03588607629265328</v>
       </c>
     </row>
     <row r="106">
@@ -2577,13 +2577,13 @@
         </is>
       </c>
       <c r="C106">
-        <v>0.6307956027835403</v>
+        <v>0.6307956027835377</v>
       </c>
       <c r="D106">
-        <v>-0.8054540118989963</v>
+        <v>-0.8054540118989959</v>
       </c>
       <c r="E106">
-        <v>0.8818203703818667</v>
+        <v>0.8818203703818686</v>
       </c>
     </row>
     <row r="107">
@@ -2598,13 +2598,13 @@
         </is>
       </c>
       <c r="C107">
-        <v>1.192807727075748</v>
+        <v>1.192807727075746</v>
       </c>
       <c r="D107">
-        <v>-0.4578868217693727</v>
+        <v>-0.4578868217693726</v>
       </c>
       <c r="E107">
-        <v>0.05765440069391963</v>
+        <v>0.05765440069392203</v>
       </c>
     </row>
     <row r="108">
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="C108">
-        <v>1.357671756759194</v>
+        <v>1.357671756759193</v>
       </c>
       <c r="D108">
-        <v>-0.3489180392285521</v>
+        <v>-0.348918039228552</v>
       </c>
       <c r="E108">
-        <v>-0.1318405980854181</v>
+        <v>-0.1318405980854154</v>
       </c>
     </row>
     <row r="109">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="C109">
-        <v>-0.1883248782001153</v>
+        <v>-0.1883248782001147</v>
       </c>
       <c r="D109">
-        <v>0.2514836750313133</v>
+        <v>0.2514836750313127</v>
       </c>
       <c r="E109">
         <v>-1.518774886317009</v>
@@ -2661,13 +2661,13 @@
         </is>
       </c>
       <c r="C110">
-        <v>-1.240288902748731</v>
+        <v>-1.240288902748732</v>
       </c>
       <c r="D110">
-        <v>0.3380419911111239</v>
+        <v>0.3380419911111242</v>
       </c>
       <c r="E110">
-        <v>-0.2893566368061781</v>
+        <v>-0.2893566368061792</v>
       </c>
     </row>
     <row r="111">
@@ -2685,10 +2685,10 @@
         <v>-1.320014841758946</v>
       </c>
       <c r="D111">
-        <v>0.5364612705361564</v>
+        <v>0.536461270536156</v>
       </c>
       <c r="E111">
-        <v>-1.491097485026754</v>
+        <v>-1.491097485026755</v>
       </c>
     </row>
     <row r="112">
@@ -2703,13 +2703,13 @@
         </is>
       </c>
       <c r="C112">
-        <v>-0.3356655127589542</v>
+        <v>-0.3356655127589557</v>
       </c>
       <c r="D112">
-        <v>0.07984336765449894</v>
+        <v>0.07984336765449918</v>
       </c>
       <c r="E112">
-        <v>-0.1063018871307647</v>
+        <v>-0.1063018871307645</v>
       </c>
     </row>
     <row r="113">
@@ -2724,13 +2724,13 @@
         </is>
       </c>
       <c r="C113">
-        <v>-0.1338166520862026</v>
+        <v>-0.1338166520862025</v>
       </c>
       <c r="D113">
-        <v>0.1741882354472054</v>
+        <v>0.1741882354472051</v>
       </c>
       <c r="E113">
-        <v>-1.091058978430011</v>
+        <v>-1.09105897843001</v>
       </c>
     </row>
     <row r="114">
@@ -2745,13 +2745,13 @@
         </is>
       </c>
       <c r="C114">
-        <v>-0.8378962599434804</v>
+        <v>-0.83789625994348</v>
       </c>
       <c r="D114">
-        <v>0.2753177402390208</v>
+        <v>0.2753177402390203</v>
       </c>
       <c r="E114">
-        <v>-1.389952184745896</v>
+        <v>-1.389952184745898</v>
       </c>
     </row>
     <row r="115">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="C115">
-        <v>-1.9895460522752</v>
+        <v>-1.989546052275201</v>
       </c>
       <c r="D115">
-        <v>0.530180767795933</v>
+        <v>0.5301807677959333</v>
       </c>
       <c r="E115">
-        <v>-0.2944109653351178</v>
+        <v>-0.2944109653351199</v>
       </c>
     </row>
     <row r="116">
@@ -2787,13 +2787,13 @@
         </is>
       </c>
       <c r="C116">
-        <v>-1.273849013515045</v>
+        <v>-1.273849013515048</v>
       </c>
       <c r="D116">
-        <v>0.2300738997046131</v>
+        <v>0.2300738997046137</v>
       </c>
       <c r="E116">
-        <v>0.4972114233331063</v>
+        <v>0.4972114233331054</v>
       </c>
     </row>
     <row r="117">
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="C117">
-        <v>0.1257602766798313</v>
+        <v>0.1257602766798297</v>
       </c>
       <c r="D117">
-        <v>-0.06809771529785873</v>
+        <v>-0.06809771529785841</v>
       </c>
       <c r="E117">
-        <v>0.09668122308299698</v>
+        <v>0.0966812230829979</v>
       </c>
     </row>
     <row r="118">
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="C118">
-        <v>-1.224640286618019</v>
+        <v>-1.22464028661802</v>
       </c>
       <c r="D118">
-        <v>0.398086353460021</v>
+        <v>0.3980863534600211</v>
       </c>
       <c r="E118">
-        <v>-0.7215929229720116</v>
+        <v>-0.7215929229720127</v>
       </c>
     </row>
     <row r="119">
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="C119">
-        <v>0.2368636347022558</v>
+        <v>0.2368636347022537</v>
       </c>
       <c r="D119">
-        <v>-0.1402210798696882</v>
+        <v>-0.1402210798696877</v>
       </c>
       <c r="E119">
-        <v>0.391917059603112</v>
+        <v>0.3919170596031131</v>
       </c>
     </row>
     <row r="120">
@@ -2871,13 +2871,13 @@
         </is>
       </c>
       <c r="C120">
-        <v>-0.332117527823359</v>
+        <v>-0.3321175278233597</v>
       </c>
       <c r="D120">
         <v>0.1458072492778337</v>
       </c>
       <c r="E120">
-        <v>-0.5576288374416256</v>
+        <v>-0.5576288374416255</v>
       </c>
     </row>
     <row r="121">
@@ -2892,13 +2892,13 @@
         </is>
       </c>
       <c r="C121">
-        <v>-0.08613420021433922</v>
+        <v>-0.08613420021434209</v>
       </c>
       <c r="D121">
-        <v>-0.1177524214579381</v>
+        <v>-0.1177524214579374</v>
       </c>
       <c r="E121">
-        <v>0.7971299927191952</v>
+        <v>0.7971299927191959</v>
       </c>
     </row>
     <row r="122">
@@ -2913,13 +2913,13 @@
         </is>
       </c>
       <c r="C122">
-        <v>-0.4244334876302606</v>
+        <v>-0.4244334876302633</v>
       </c>
       <c r="D122">
-        <v>-0.01202209104416042</v>
+        <v>-0.01202209104415974</v>
       </c>
       <c r="E122">
-        <v>0.6667651366642603</v>
+        <v>0.6667651366642606</v>
       </c>
     </row>
     <row r="123">
@@ -2934,13 +2934,13 @@
         </is>
       </c>
       <c r="C123">
-        <v>1.220838487621557</v>
+        <v>1.220838487621556</v>
       </c>
       <c r="D123">
         <v>-0.4351974996589947</v>
       </c>
       <c r="E123">
-        <v>-0.1438087698339119</v>
+        <v>-0.1438087698339094</v>
       </c>
     </row>
     <row r="124">
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="C124">
-        <v>0.7554841074045214</v>
+        <v>0.755484107404519</v>
       </c>
       <c r="D124">
-        <v>-0.3241497589456629</v>
+        <v>-0.3241497589456622</v>
       </c>
       <c r="E124">
-        <v>0.7391854558507041</v>
+        <v>0.7391854558507061</v>
       </c>
     </row>
     <row r="125">
@@ -2976,13 +2976,13 @@
         </is>
       </c>
       <c r="C125">
-        <v>0.4256129091825256</v>
+        <v>0.4256129091825233</v>
       </c>
       <c r="D125">
-        <v>-0.2162436751700585</v>
+        <v>-0.2162436751700579</v>
       </c>
       <c r="E125">
-        <v>0.5796054361867604</v>
+        <v>0.579605436186762</v>
       </c>
     </row>
     <row r="126">
@@ -2997,13 +2997,13 @@
         </is>
       </c>
       <c r="C126">
-        <v>-0.07329420397286458</v>
+        <v>-0.07329420397286773</v>
       </c>
       <c r="D126">
-        <v>-0.1622705968489721</v>
+        <v>-0.1622705968489712</v>
       </c>
       <c r="E126">
-        <v>1.075459909023067</v>
+        <v>1.075459909023068</v>
       </c>
     </row>
   </sheetData>
